--- a/05-halcyon-ai-governance/artifacts/ai_system_inventory.xlsx
+++ b/05-halcyon-ai-governance/artifacts/ai_system_inventory.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Classification Method" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'AI System Inventory'!$A$1:$S$13</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'AI System Inventory'!$A$1:$U$13</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">'Classification Method'!$A$1:$B$9</definedName>
-    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Summary!$A$1:$B$18</definedName>
+    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Summary!$A$1:$B$19</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,12 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="179">
   <si>
     <t xml:space="preserve">HALCYON BENEFITS GROUP — AI SYSTEM INVENTORY &amp; RISK CLASSIFICATION</t>
   </si>
   <si>
-    <t xml:space="preserve">Sample GRC portfolio artifact | Fictional company | Framework basis: NIST AI RMF 1.0 (Map function), EU AI Act risk tiers, ISO/IEC 42001 A.4 | Inventory date: 2026-07-15</t>
+    <t xml:space="preserve">Sample GRC portfolio artifact | Fictional company | Framework basis: NIST AI RMF 1.0 (Map), EU AI Act as amended by Regulation (EU) 2026/1744 (Digital Omnibus on AI, in force 27 July 2026), ISO/IEC 42001 A.4 | Inventory date: 2026-08-05</t>
   </si>
   <si>
     <t xml:space="preserve">AI ID</t>
@@ -74,12 +74,18 @@
     <t xml:space="preserve">EU Nexus?</t>
   </si>
   <si>
-    <t xml:space="preserve">EU AI Act Tier (assessed)</t>
+    <t xml:space="preserve">EU AI Act Tier (legal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applicable Deadline</t>
   </si>
   <si>
     <t xml:space="preserve">EU Act Rationale</t>
   </si>
   <si>
+    <t xml:space="preserve">Organizational Risk Flag</t>
+  </si>
+  <si>
     <t xml:space="preserve">NIST AI RMF Profile Applied</t>
   </si>
   <si>
@@ -131,148 +137,166 @@
     <t xml:space="preserve">Yes — 3 EU-based client plans</t>
   </si>
   <si>
+    <t xml:space="preserve">High-Risk (contested)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 Dec 2027 if confirmed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTESTED. Annex III(5)(a) covers essential PUBLIC assistance benefits by public authorities — Halcyon is a private administrator. Annex III(5)(c) covers risk assessment and pricing for life/health insurance — this is claims adjudication, not pricing. Neither category fits cleanly. Treated as high-risk pending counsel determination; see Risk AIR-004 for both classification outcomes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI RMF Core + fairness testing profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ungoverned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority 1: obtain counsel determination on Annex III applicability; proceed with fairness testing regardless (see Decision Memo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Member Support Chatbot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of Member Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Answers plan questions, routes to agents; GenAI over plan documents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generative (LLM, RAG)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure OpenAI GPT-4o over indexed plan docs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy + configure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Member questions, plan documents, limited account context</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Informational; can misdirect on coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human-on-the-loop (escalation available)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limited-Risk (transparency)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 Aug 2026 — NOT DEFERRED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Art. 50 transparency duties apply to systems interacting with natural persons. The Digital Omnibus deferred Annex III high-risk deadlines but expressly did NOT defer Art. 50. This is the most time-critical item in the inventory.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI RMF Core + Generative AI Profile (AI 600-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partially governed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deploy AI disclosure immediately (deadline passed); implement confabulation testing; log and sample coverage answers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fraud Pattern Detector</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of SIU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flags claims for special investigation review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Predictive ML (anomaly)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Third-party SaaS (VigilAI)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claims data, provider billing patterns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Triggers investigation; may delay payment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human-on-the-loop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Out of EU scope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No EU nexus. If scope expands to EU plans, re-assess against Annex III.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI RMF Core</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendor AI questionnaire; document oversight; re-assess on any EU expansion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recruiting Resume Screener</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VP People</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranks applicants for benefits-analyst roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pilot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Predictive ML (NLP scoring)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Third-party ATS module</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resumes, application forms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Affects hiring shortlist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human-in-the-loop (recruiter reviews top 20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes — EU-based recruiting for Dublin office</t>
+  </si>
+  <si>
     <t xml:space="preserve">High-Risk</t>
   </si>
   <si>
-    <t xml:space="preserve">Access to essential private services (insurance/benefits eligibility) — Annex III category; automated recommendation materially influences outcome. Human confirmation reduces but does not eliminate high-risk classification.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI RMF Core + fairness testing profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ungoverned</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority 1: full risk assessment, bias audit, oversight redesign, EU conformity path (see AI Risk Assessment)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI-002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Member Support Chatbot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of Member Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Answers plan questions, routes to agents; GenAI over plan documents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generative (LLM, RAG)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure OpenAI GPT-4o over indexed plan docs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buy + configure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Member questions, plan documents, limited account context</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Informational; can misdirect on coverage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Human-on-the-loop (escalation available)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Limited-Risk (transparency)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interacts with natural persons; must disclose AI nature. Not making eligibility decisions itself, but confabulated coverage answers create indirect harm.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI RMF Core + Generative AI Profile (AI 600-1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partially governed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add AI disclosure banner; implement confabulation testing; log and sample review of coverage-related answers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI-003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fraud Pattern Detector</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of SIU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flags claims for special investigation review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Predictive ML (anomaly)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Third-party SaaS (VigilAI)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claims data, provider billing patterns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Triggers investigation; may delay payment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Human-on-the-loop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minimal / not in EU scope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No EU nexus; if scope expands to EU plans, likely High-Risk under Annex III (essential services).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI RMF Core</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vendor AI questionnaire; document oversight; monitor for EU expansion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI-004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recruiting Resume Screener</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VP People</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ranks applicants for benefits-analyst roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pilot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Predictive ML (NLP scoring)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Third-party ATS module</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resumes, application forms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Affects hiring shortlist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Human-in-the-loop (recruiter reviews top 20)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes — EU-based recruiting for Dublin office</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employment / worker management — explicit Annex III category. Also NYC Local Law 144 exposure for NYC roles.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority 1: pause pilot pending bias audit and vendor assessment (see AI Risk Assessment)</t>
+    <t xml:space="preserve">2 Dec 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLEAR. Annex III(4)(a) — AI intended for recruitment or selection, in particular to filter applications and evaluate candidates. Unambiguous. Also NYC Local Law 144 exposure for NYC roles, which has no EU deadline dependency.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority 1: pause pilot pending bias audit and vendor transparency documentation (see Decision Memo)</t>
   </si>
   <si>
     <t xml:space="preserve">AI-005</t>
@@ -344,13 +368,13 @@
     <t xml:space="preserve">Human-in-the-loop</t>
   </si>
   <si>
-    <t xml:space="preserve">No personal data; all output human-reviewed before publication.</t>
+    <t xml:space="preserve">No personal data; all output human-reviewed before publication. Note Art. 50(4) synthetic-content marking may apply if AI-generated imagery is published.</t>
   </si>
   <si>
     <t xml:space="preserve">Generative AI Profile (light)</t>
   </si>
   <si>
-    <t xml:space="preserve">Acceptable use policy attestation; keep in inventory</t>
+    <t xml:space="preserve">Acceptable use attestation; monitor for synthetic-media marking obligations</t>
   </si>
   <si>
     <t xml:space="preserve">AI-007</t>
@@ -374,16 +398,16 @@
     <t xml:space="preserve">Productivity; data exposure risk</t>
   </si>
   <si>
-    <t xml:space="preserve">Minimal (system) / Data risk (organizational)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not a high-risk use case, but broad access to sensitive data creates data governance exposure. Governance issue is DLP and access scoping, not AI Act tier.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generative AI Profile — data privacy &amp; information integrity risks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restrict Copilot indexing of PHI repositories; DLP policy for AI-generated content; usage attestation</t>
+    <t xml:space="preserve">Not a high-risk use case under the Act. The exposure here is data governance, not AI Act classification — tracked separately in the Organizational Risk Flag column.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HIGH — broad access to PHI repositories creates HIPAA exposure independent of AI Act status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generative AI Profile — data privacy &amp; information integrity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restrict Copilot indexing of PHI repositories; DLP for AI-generated content; usage attestation</t>
   </si>
   <si>
     <t xml:space="preserve">AI-008</t>
@@ -413,67 +437,73 @@
     <t xml:space="preserve">Pricing decisions; indirect member impact</t>
   </si>
   <si>
-    <t xml:space="preserve">Aggregate data, expert-reviewed outputs; model risk governance applies (SR 11-7 style), not AI Act.</t>
+    <t xml:space="preserve">Aggregate data, expert-reviewed outputs. NOTE: if this model were applied to individual health-insurance risk assessment or pricing, Annex III(5)(c) would apply. It is not, today.</t>
   </si>
   <si>
     <t xml:space="preserve">AI RMF Core + model risk management</t>
   </si>
   <si>
-    <t xml:space="preserve">Annual model validation; align to model risk policy</t>
+    <t xml:space="preserve">Annual model validation; re-assess if scope moves to individual pricing</t>
   </si>
   <si>
     <t xml:space="preserve">AI-009</t>
   </si>
   <si>
-    <t xml:space="preserve">Shadow AI — unsanctioned tools</t>
+    <t xml:space="preserve">Shadow AI (governance finding)</t>
   </si>
   <si>
     <t xml:space="preserve">CISO (owner by default)</t>
   </si>
   <si>
-    <t xml:space="preserve">Various staff using consumer AI tools with work data</t>
+    <t xml:space="preserve">Unsanctioned consumer AI tool use with work data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not a system — enterprise finding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generative (various)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumer ChatGPT, Gemini, Claude free tiers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unmanaged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown; likely includes member data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Likely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data leakage; policy violation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None</t>
   </si>
   <si>
     <t xml:space="preserve">Unknown</t>
   </si>
   <si>
-    <t xml:space="preserve">Generative (various)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumer ChatGPT, Gemini, Claude free tiers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neither — unmanaged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unknown; likely includes member data in some cases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Likely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data leakage; policy violation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">None</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not applicable (organizational risk)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not a system; a governance gap. Discovered via CASB telemetry: 214 unique users hitting consumer AI endpoints in 30 days.</t>
+    <t xml:space="preserve">N/A — governance finding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not an AI system and therefore not classifiable under the Act. Recorded here because an inventory that omits known unmanaged use is not an inventory. Discovered via CASB telemetry: 214 unique users hitting consumer AI endpoints in 30 days.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRITICAL — uncontrolled PHI egress to third-party models with no DPA or contractual protection</t>
   </si>
   <si>
     <t xml:space="preserve">AI RMF Govern function</t>
   </si>
   <si>
-    <t xml:space="preserve">Acceptable use policy; CASB blocking of consumer tiers; sanctioned alternative (AI-007); awareness campaign</t>
+    <t xml:space="preserve">Acceptable use policy; CASB blocking; sanctioned alternative (AI-007); awareness campaign</t>
   </si>
   <si>
     <t xml:space="preserve">INVENTORY SUMMARY</t>
   </si>
   <si>
-    <t xml:space="preserve">Counts derived from the inventory tab. Note: 9 rows includes one governance gap (AI-009) that is not a discrete system.</t>
+    <t xml:space="preserve">Eight identified AI systems plus one enterprise shadow-AI governance finding (AI-009). Counts total 9 rows; AI-009 is not a discrete system and is not classifiable under the AI Act.</t>
   </si>
   <si>
     <t xml:space="preserve">EU AI Act Tier</t>
@@ -482,13 +512,13 @@
     <t xml:space="preserve">Count</t>
   </si>
   <si>
-    <t xml:space="preserve">Systems with personal data</t>
+    <t xml:space="preserve">Entries flagged for personal data</t>
   </si>
   <si>
     <t xml:space="preserve">Systems with EU nexus</t>
   </si>
   <si>
-    <t xml:space="preserve">High-Risk AND Ungoverned (Priority 1)</t>
+    <t xml:space="preserve">High-Risk (incl. contested) AND Ungoverned</t>
   </si>
   <si>
     <t xml:space="preserve">HOW SYSTEMS WERE CLASSIFIED</t>
@@ -742,7 +772,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="7">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -754,6 +784,20 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE06666"/>
         </patternFill>
       </fill>
     </dxf>
@@ -781,6 +825,33 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF70AD47"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB7B7B7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF808080"/>
         </patternFill>
       </fill>
     </dxf>
@@ -815,7 +886,7 @@
       <rgbColor rgb="FFFFFFCC"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FFE06666"/>
       <rgbColor rgb="FF0066CC"/>
       <rgbColor rgb="FFCCCCFF"/>
       <rgbColor rgb="FF000080"/>
@@ -1035,7 +1106,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -1051,12 +1122,14 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="32"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1081,6 +1154,8 @@
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
@@ -1104,6 +1179,8 @@
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
       <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
@@ -1163,576 +1240,655 @@
       <c r="S4" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L5" s="4" t="s">
+      <c r="F6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J6" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="M5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="R5" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="S5" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="K6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q6" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q6" s="4" t="n">
+      <c r="R6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="S6" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="R6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="S6" s="4" t="s">
-        <v>53</v>
+      <c r="T6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="U6" s="4" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R7" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="S7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="N7" s="4" t="s">
+      <c r="U7" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="O7" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="P7" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="S7" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>60</v>
-      </c>
       <c r="I8" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q8" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="S8" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="R8" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="S8" s="4" t="s">
-        <v>81</v>
+      <c r="T8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="U8" s="4" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="J9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="P9" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R9" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="U9" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="O10" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="P10" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R10" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="S10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="U10" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="O11" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="P11" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q11" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="R11" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="S11" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="U11" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="K9" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="N9" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="O9" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R9" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="S9" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="I12" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="N12" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="I10" s="4" t="s">
+      <c r="O12" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="P12" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R12" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="S12" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="J10" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="N10" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="O10" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="P10" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q10" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="S10" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="N11" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="O11" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="P11" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q11" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="S11" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="M12" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="N12" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="O12" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="P12" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q12" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R12" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="S12" s="4" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="U12" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>144</v>
+        <v>71</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q13" s="4" t="n">
+        <v>153</v>
+      </c>
+      <c r="Q13" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="R13" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="S13" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="R13" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="S13" s="4" t="s">
-        <v>146</v>
+      <c r="T13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="U13" s="4" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A2:U2"/>
   </mergeCells>
   <conditionalFormatting sqref="N5:N13">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>EXACT(N5,"High-Risk")</formula>
     </cfRule>
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>EXACT(N5,"High-Risk (contested)")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>EXACT(N5,"Limited-Risk (transparency)")</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>EXACT(N5,"Minimal")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+      <formula>EXACT(N5,"Out of EU scope")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+      <formula>EXACT(N5,"N/A — governance finding")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O5:O13">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>ISNUMBER(SEARCH("NOT DEFERRED",O5))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5:R13">
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>EXACT(R5,"Ungoverned")</formula>
-    </cfRule>
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>EXACT(R5,"Partially governed")</formula>
-    </cfRule>
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
-      <formula>EXACT(R5,"Governed")</formula>
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+      <formula>OR(LEFT(R5,4)="HIGH",LEFT(R5,8)="CRITICAL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q5:Q13">
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
-      <formula>Q5&gt;=4</formula>
+  <conditionalFormatting sqref="T5:T13">
+    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>EXACT(T5,"Ungoverned")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>EXACT(T5,"Partially governed")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>EXACT(T5,"Governed")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S5:S13">
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+      <formula>S5&gt;=4</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="N5:N43" type="list">
-      <formula1>"Unacceptable-Risk (prohibited),High-Risk,Limited-Risk (transparency),Minimal,Minimal / not in EU scope,Not applicable (organizational risk)"</formula1>
+      <formula1>"Unacceptable-Risk (prohibited),High-Risk,High-Risk (contested),Limited-Risk (transparency),Minimal,Out of EU scope,N/A — governance finding"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="R5:R43" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="T5:T43" type="list">
       <formula1>"Ungoverned,Partially governed,Governed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -1752,7 +1908,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
@@ -1761,34 +1917,34 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="B5" s="4" t="n">
         <f aca="false">COUNTIF('AI System Inventory'!$N$5:$N$13,A5)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B6" s="4" t="n">
         <f aca="false">COUNTIF('AI System Inventory'!$N$5:$N$13,A6)</f>
@@ -1797,90 +1953,99 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>91</v>
+        <v>53</v>
       </c>
       <c r="B7" s="4" t="n">
         <f aca="false">COUNTIF('AI System Inventory'!$N$5:$N$13,A7)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="B8" s="4" t="n">
         <f aca="false">COUNTIF('AI System Inventory'!$N$5:$N$13,A8)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>143</v>
+        <v>70</v>
       </c>
       <c r="B9" s="4" t="n">
         <f aca="false">COUNTIF('AI System Inventory'!$N$5:$N$13,A9)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>150</v>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <f aca="false">COUNTIF('AI System Inventory'!$N$5:$N$13,A10)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="4" t="n">
-        <f aca="false">COUNTIF('AI System Inventory'!$R$5:$R$13,A12)</f>
-        <v>3</v>
+      <c r="A12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B13" s="4" t="n">
-        <f aca="false">COUNTIF('AI System Inventory'!$R$5:$R$13,A13)</f>
+        <f aca="false">COUNTIF('AI System Inventory'!$T$5:$T$13,A13)</f>
         <v>3</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="B14" s="4" t="n">
-        <f aca="false">COUNTIF('AI System Inventory'!$R$5:$R$13,A14)</f>
+        <f aca="false">COUNTIF('AI System Inventory'!$T$5:$T$13,A14)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="B16" s="8" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <f aca="false">COUNTIF('AI System Inventory'!$T$5:$T$13,A15)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="B17" s="8" t="n">
         <f aca="false">COUNTIF('AI System Inventory'!$J$5:$J$13,"Yes")</f>
         <v>6</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="B17" s="8" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B18" s="8" t="n">
         <f aca="false">COUNTIF('AI System Inventory'!$M$5:$M$13,"Yes*")</f>
         <v>5</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="B18" s="8" t="n">
-        <f aca="false">COUNTIFS('AI System Inventory'!$N$5:$N$13,"High-Risk",'AI System Inventory'!$R$5:$R$13,"Ungoverned")</f>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="B19" s="8" t="n">
+        <f aca="false">COUNTIFS('AI System Inventory'!$N$5:$N$13,"High-Risk*",'AI System Inventory'!$T$5:$T$13,"Ungoverned")</f>
         <v>2</v>
       </c>
     </row>
@@ -1909,63 +2074,63 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
